--- a/southern_europe/italy_data/geographical_feature/node_metrics_paper.xlsx
+++ b/southern_europe/italy_data/geographical_feature/node_metrics_paper.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0954659\PycharmProjects\AdOpT-NET0_luca\southern_europe\italy_data\geographical_feature\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69341046-F97C-4F12-B9DE-DBBCB35D9458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{789CA20E-FBC3-488D-8312-AF6E5685BDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="nodes" sheetId="1" r:id="rId1"/>
@@ -22,14 +22,27 @@
     <sheet name="truck_availability" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">nodes!$H$1:$H$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">nodes!$H$1:$H$48</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="173">
   <si>
     <t>node_id</t>
   </si>
@@ -152,9 +165,6 @@
   </si>
   <si>
     <t>Ferrara</t>
-  </si>
-  <si>
-    <t>Fertilizers</t>
   </si>
   <si>
     <t>FRULLO ENERGIA AMBIENTE S.R.L.</t>
@@ -545,6 +555,12 @@
   </si>
   <si>
     <t>Hypothetical potential transport switch</t>
+  </si>
+  <si>
+    <t>FertilizersCombustion</t>
+  </si>
+  <si>
+    <t>FertilizersSMR</t>
   </si>
 </sst>
 </file>
@@ -979,7 +995,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I999"/>
+  <dimension ref="A1:I1000"/>
   <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5" customWidth="1"/>
@@ -1814,163 +1830,165 @@
         <v>10</v>
       </c>
       <c r="F32" s="29">
-        <v>646992</v>
+        <f>646992*0.75</f>
+        <v>485244</v>
       </c>
       <c r="G32" s="29">
         <v>0</v>
       </c>
       <c r="H32" s="30" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="4">
-        <v>30</v>
-      </c>
-      <c r="B33" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="C33" s="2">
-        <v>11.428890000000001</v>
-      </c>
-      <c r="D33" s="2">
-        <v>44.522860000000001</v>
-      </c>
-      <c r="E33" s="4">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" s="29" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <v>29</v>
+      </c>
+      <c r="B33" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="C33" s="28">
+        <v>11.569093000000001</v>
+      </c>
+      <c r="D33" s="28">
+        <v>44.8611073</v>
+      </c>
+      <c r="E33" s="27">
         <v>10</v>
       </c>
-      <c r="F33">
-        <v>186972</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>9</v>
+      <c r="F33" s="29">
+        <f>646992*0.25</f>
+        <v>161748</v>
+      </c>
+      <c r="G33" s="29">
+        <v>0</v>
+      </c>
+      <c r="H33" s="30" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C34" s="2">
-        <v>11.75079</v>
+        <v>11.428890000000001</v>
       </c>
       <c r="D34" s="2">
-        <v>45.252960000000002</v>
+        <v>44.522860000000001</v>
       </c>
       <c r="E34" s="4">
         <v>10</v>
       </c>
       <c r="F34">
-        <v>342306</v>
+        <v>186972</v>
       </c>
       <c r="G34">
-        <v>342306</v>
+        <v>0</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="C35" s="5">
-        <v>10.825699999999999</v>
-      </c>
-      <c r="D35" s="5">
-        <v>45.564</v>
+        <v>42</v>
+      </c>
+      <c r="C35" s="2">
+        <v>11.75079</v>
+      </c>
+      <c r="D35" s="2">
+        <v>45.252960000000002</v>
       </c>
       <c r="E35" s="4">
         <v>10</v>
       </c>
       <c r="F35">
-        <v>126945</v>
+        <v>342306</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>342306</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="C36" s="2">
-        <v>11.963570000000001</v>
-      </c>
-      <c r="D36" s="2">
-        <v>45.88</v>
+        <v>43</v>
+      </c>
+      <c r="C36" s="5">
+        <v>10.825699999999999</v>
+      </c>
+      <c r="D36" s="5">
+        <v>45.564</v>
       </c>
       <c r="E36" s="4">
         <v>10</v>
       </c>
       <c r="F36">
-        <v>351766</v>
+        <v>126945</v>
       </c>
       <c r="G36">
         <v>0</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C37" s="2">
-        <v>11.924099999999999</v>
+        <v>11.963570000000001</v>
       </c>
       <c r="D37" s="2">
-        <v>45.408700000000003</v>
+        <v>45.88</v>
       </c>
       <c r="E37" s="4">
         <v>10</v>
       </c>
       <c r="F37">
-        <v>179315.79300000001</v>
+        <v>351766</v>
       </c>
       <c r="G37">
         <v>0</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C38" s="2">
-        <v>12.08798</v>
+        <v>11.924099999999999</v>
       </c>
       <c r="D38" s="2">
-        <v>44.234389999999998</v>
+        <v>45.408700000000003</v>
       </c>
       <c r="E38" s="4">
         <v>10</v>
       </c>
       <c r="F38">
-        <v>144055</v>
+        <v>179315.79300000001</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -1979,154 +1997,154 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:8" s="31" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="33">
+    <row r="39" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="4">
+        <v>35</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C39" s="2">
+        <v>12.08798</v>
+      </c>
+      <c r="D39" s="2">
+        <v>44.234389999999998</v>
+      </c>
+      <c r="E39" s="4">
+        <v>10</v>
+      </c>
+      <c r="F39">
+        <v>144055</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" s="31" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="33">
         <v>36</v>
       </c>
-      <c r="B39" s="32" t="s">
-        <v>49</v>
-      </c>
-      <c r="C39" s="35">
+      <c r="B40" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40" s="35">
         <v>12.269209999999999</v>
       </c>
-      <c r="D39" s="35">
+      <c r="D40" s="35">
         <v>45.816160000000004</v>
       </c>
-      <c r="E39" s="33">
+      <c r="E40" s="33">
         <v>10</v>
       </c>
-      <c r="F39" s="31">
+      <c r="F40" s="31">
         <v>197108</v>
       </c>
-      <c r="G39" s="31">
-        <v>0</v>
-      </c>
-      <c r="H39" s="34" t="s">
+      <c r="G40" s="31">
+        <v>0</v>
+      </c>
+      <c r="H40" s="34" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="4">
-        <v>37</v>
-      </c>
-      <c r="B40" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="C40" s="2">
-        <v>12.2</v>
-      </c>
-      <c r="D40" s="2">
-        <v>44.41</v>
-      </c>
-      <c r="E40" s="6">
-        <v>10</v>
-      </c>
-      <c r="F40">
-        <v>500000</v>
-      </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
-        <v>38</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C41" s="5">
-        <v>12.241742</v>
-      </c>
-      <c r="D41" s="5">
-        <v>45.467055999999999</v>
-      </c>
-      <c r="E41" s="4">
+        <v>37</v>
+      </c>
+      <c r="B41" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C41" s="2">
+        <v>12.2</v>
+      </c>
+      <c r="D41" s="2">
+        <v>44.41</v>
+      </c>
+      <c r="E41" s="6">
         <v>10</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="G41">
         <v>0</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
-        <v>39</v>
-      </c>
-      <c r="B42" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="C42" s="2">
-        <v>12.74245</v>
-      </c>
-      <c r="D42" s="2">
-        <v>46.17642</v>
+        <v>38</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C42" s="5">
+        <v>12.241742</v>
+      </c>
+      <c r="D42" s="5">
+        <v>45.467055999999999</v>
       </c>
       <c r="E42" s="4">
         <v>10</v>
       </c>
       <c r="F42">
-        <v>438034</v>
+        <v>0</v>
       </c>
       <c r="G42">
-        <v>438034</v>
+        <v>0</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C43" s="2">
-        <v>12.63189</v>
+        <v>12.74245</v>
       </c>
       <c r="D43" s="2">
-        <v>43.9803</v>
+        <v>46.17642</v>
       </c>
       <c r="E43" s="4">
         <v>10</v>
       </c>
       <c r="F43">
-        <v>128100.192</v>
+        <v>438034</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>438034</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C44" s="2">
-        <v>13.80006</v>
+        <v>12.63189</v>
       </c>
       <c r="D44" s="2">
-        <v>45.611739999999998</v>
+        <v>43.9803</v>
       </c>
       <c r="E44" s="4">
         <v>10</v>
       </c>
       <c r="F44">
-        <v>157981.171</v>
+        <v>128100.192</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -2137,42 +2155,42 @@
     </row>
     <row r="45" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C45" s="2">
-        <v>12.274480000000001</v>
+        <v>13.80006</v>
       </c>
       <c r="D45" s="2">
-        <v>44.560099999999998</v>
-      </c>
-      <c r="E45" s="6">
+        <v>45.611739999999998</v>
+      </c>
+      <c r="E45" s="4">
         <v>10</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>157981.171</v>
       </c>
       <c r="G45">
         <v>0</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="C46" s="5">
-        <v>12.564</v>
-      </c>
-      <c r="D46" s="5">
-        <v>44.387</v>
+        <v>55</v>
+      </c>
+      <c r="C46" s="2">
+        <v>12.274480000000001</v>
+      </c>
+      <c r="D46" s="2">
+        <v>44.560099999999998</v>
       </c>
       <c r="E46" s="6">
         <v>10</v>
@@ -2184,125 +2202,147 @@
         <v>0</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
+        <v>43</v>
+      </c>
+      <c r="B47" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C47" s="5">
+        <v>12.564</v>
+      </c>
+      <c r="D47" s="5">
+        <v>44.387</v>
+      </c>
+      <c r="E47" s="6">
+        <v>10</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="4">
         <v>44</v>
       </c>
-      <c r="B47" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C47" s="4">
+      <c r="B48" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="4">
         <v>10.64</v>
       </c>
-      <c r="D47" s="4">
+      <c r="D48" s="4">
         <v>44.96</v>
-      </c>
-      <c r="E47" s="4">
-        <v>10</v>
-      </c>
-      <c r="F47">
-        <v>0</v>
-      </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>45</v>
-      </c>
-      <c r="B48" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="C48" s="24">
-        <v>9.6260580000000004</v>
-      </c>
-      <c r="D48" s="24">
-        <v>45.789459999999998</v>
       </c>
       <c r="E48" s="4">
         <v>10</v>
       </c>
       <c r="F48">
-        <v>244453</v>
+        <v>0</v>
       </c>
       <c r="G48">
         <v>0</v>
       </c>
-      <c r="H48" s="1" t="s">
-        <v>45</v>
+      <c r="H48" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C49" s="24">
-        <v>10.3314</v>
+        <v>9.6260580000000004</v>
       </c>
       <c r="D49" s="24">
-        <v>45.459499999999998</v>
+        <v>45.789459999999998</v>
       </c>
       <c r="E49" s="4">
         <v>10</v>
       </c>
       <c r="F49">
-        <v>203184</v>
+        <v>244453</v>
       </c>
       <c r="G49">
         <v>0</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I49" s="23"/>
+        <v>44</v>
+      </c>
     </row>
     <row r="50" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C50" s="24">
-        <v>7.4390000000000001</v>
+        <v>10.3314</v>
       </c>
       <c r="D50" s="24">
-        <v>44.384</v>
+        <v>45.459499999999998</v>
       </c>
       <c r="E50" s="4">
         <v>10</v>
       </c>
       <c r="F50">
+        <v>203184</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I50" s="23"/>
+    </row>
+    <row r="51" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>47</v>
+      </c>
+      <c r="B51" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C51" s="24">
+        <v>7.4390000000000001</v>
+      </c>
+      <c r="D51" s="24">
+        <v>44.384</v>
+      </c>
+      <c r="E51" s="4">
+        <v>10</v>
+      </c>
+      <c r="F51">
         <v>139988</v>
       </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I50" s="23"/>
-    </row>
-    <row r="51" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="I51" s="23"/>
     </row>
-    <row r="52" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
-    </row>
+    <row r="52" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="I52" s="23"/>
+    </row>
+    <row r="53" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="54" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
@@ -6087,8 +6127,12 @@
       <c r="C999" s="5"/>
       <c r="D999" s="5"/>
     </row>
+    <row r="1000" spans="3:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C1000" s="5"/>
+      <c r="D1000" s="5"/>
+    </row>
   </sheetData>
-  <autoFilter ref="H1:H47" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="H1:H48" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -30300,45 +30344,45 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="C1" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="E1" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="F1" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="G1" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="H1" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="I1" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="J1" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="K1" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="L1" s="12" t="s">
         <v>73</v>
-      </c>
-      <c r="L1" s="12" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B2" s="15">
         <v>11.75079</v>
@@ -30353,25 +30397,25 @@
         <v>11</v>
       </c>
       <c r="F2" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="G2" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="H2" s="14" t="s">
         <v>76</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>77</v>
       </c>
       <c r="I2" s="14">
         <v>800000</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K2" s="14">
         <v>2021</v>
       </c>
       <c r="L2" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M2" s="18"/>
       <c r="N2" s="18"/>
@@ -30390,7 +30434,7 @@
     </row>
     <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B3" s="15">
         <v>11.963570000000001</v>
@@ -30405,13 +30449,13 @@
         <v>11</v>
       </c>
       <c r="F3" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="G3" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="H3" s="14" t="s">
         <v>81</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>82</v>
       </c>
       <c r="I3" s="14">
         <v>1000000</v>
@@ -30421,7 +30465,7 @@
         <v>2021</v>
       </c>
       <c r="L3" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M3" s="18"/>
       <c r="N3" s="18"/>
@@ -30440,7 +30484,7 @@
     </row>
     <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B4" s="15">
         <v>12.269209999999999</v>
@@ -30455,23 +30499,23 @@
         <v>11</v>
       </c>
       <c r="F4" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="H4" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="G4" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="H4" s="14" t="s">
+      <c r="I4" s="14" t="s">
         <v>84</v>
-      </c>
-      <c r="I4" s="14" t="s">
-        <v>85</v>
       </c>
       <c r="J4" s="14"/>
       <c r="K4" s="14">
         <v>2021</v>
       </c>
       <c r="L4" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M4" s="18"/>
       <c r="N4" s="18"/>
@@ -30505,25 +30549,25 @@
         <v>11</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I5" s="14">
         <v>1600000</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K5" s="14">
         <v>2021</v>
       </c>
       <c r="L5" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M5" s="18"/>
       <c r="N5" s="18"/>
@@ -30557,13 +30601,13 @@
         <v>11</v>
       </c>
       <c r="F6" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="G6" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="H6" s="14" t="s">
         <v>88</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>89</v>
       </c>
       <c r="I6" s="14"/>
       <c r="J6" s="14"/>
@@ -30571,7 +30615,7 @@
         <v>2021</v>
       </c>
       <c r="L6" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M6" s="18"/>
       <c r="N6" s="18"/>
@@ -30605,25 +30649,25 @@
         <v>11</v>
       </c>
       <c r="F7" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="H7" s="14" t="s">
         <v>90</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>91</v>
       </c>
       <c r="I7" s="14">
         <v>1500000</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K7" s="14">
         <v>2021</v>
       </c>
       <c r="L7" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M7" s="18"/>
       <c r="N7" s="18"/>
@@ -30657,21 +30701,21 @@
         <v>11</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G8" s="14"/>
       <c r="H8" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J8" s="14"/>
       <c r="K8" s="14">
         <v>2021</v>
       </c>
       <c r="L8" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M8" s="18"/>
       <c r="N8" s="18"/>
@@ -30705,25 +30749,25 @@
         <v>11</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I9" s="14">
         <v>1300000</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K9" s="14">
         <v>2021</v>
       </c>
       <c r="L9" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M9" s="18"/>
       <c r="N9" s="18"/>
@@ -30757,23 +30801,23 @@
         <v>11</v>
       </c>
       <c r="F10" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="H10" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="G10" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="H10" s="14" t="s">
-        <v>96</v>
-      </c>
       <c r="I10" s="14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J10" s="14"/>
       <c r="K10" s="14">
         <v>2021</v>
       </c>
       <c r="L10" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M10" s="18"/>
       <c r="N10" s="18"/>
@@ -30807,23 +30851,23 @@
         <v>11</v>
       </c>
       <c r="F11" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="H11" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="G11" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>98</v>
-      </c>
       <c r="I11" s="14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J11" s="14"/>
       <c r="K11" s="14">
         <v>2021</v>
       </c>
       <c r="L11" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M11" s="18"/>
       <c r="N11" s="18"/>
@@ -30842,7 +30886,7 @@
     </row>
     <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B12" s="15">
         <v>12.74245</v>
@@ -30857,25 +30901,25 @@
         <v>11</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I12" s="14">
         <v>1000000</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K12" s="14">
         <v>2021</v>
       </c>
       <c r="L12" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M12" s="18"/>
       <c r="N12" s="18"/>
@@ -30894,7 +30938,7 @@
     </row>
     <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B13" s="15">
         <v>9.7164300000000008</v>
@@ -30909,13 +30953,13 @@
         <v>11</v>
       </c>
       <c r="F13" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="G13" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="G13" s="14" t="s">
-        <v>81</v>
-      </c>
       <c r="H13" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I13" s="14">
         <v>1000000</v>
@@ -30925,7 +30969,7 @@
         <v>2021</v>
       </c>
       <c r="L13" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M13" s="18"/>
       <c r="N13" s="18"/>
@@ -30959,25 +31003,25 @@
         <v>11</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I14" s="14">
         <v>1300000</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K14" s="14">
         <v>2021</v>
       </c>
       <c r="L14" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M14" s="18"/>
       <c r="N14" s="18"/>
@@ -31012,10 +31056,10 @@
       </c>
       <c r="F15" s="14"/>
       <c r="G15" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="H15" s="14" t="s">
         <v>103</v>
-      </c>
-      <c r="H15" s="14" t="s">
-        <v>104</v>
       </c>
       <c r="I15" s="14"/>
       <c r="J15" s="14"/>
@@ -31023,7 +31067,7 @@
         <v>2021</v>
       </c>
       <c r="L15" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M15" s="18"/>
       <c r="N15" s="18"/>
@@ -31057,13 +31101,13 @@
         <v>18</v>
       </c>
       <c r="F16" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="H16" s="14" t="s">
         <v>105</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>106</v>
       </c>
       <c r="I16" s="14"/>
       <c r="J16" s="14"/>
@@ -31071,7 +31115,7 @@
         <v>2021</v>
       </c>
       <c r="L16" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M16" s="18"/>
       <c r="N16" s="18"/>
@@ -31105,13 +31149,13 @@
         <v>18</v>
       </c>
       <c r="F17" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="H17" s="14" t="s">
         <v>107</v>
-      </c>
-      <c r="G17" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="H17" s="14" t="s">
-        <v>108</v>
       </c>
       <c r="I17" s="14"/>
       <c r="J17" s="14"/>
@@ -31119,7 +31163,7 @@
         <v>2021</v>
       </c>
       <c r="L17" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M17" s="18"/>
       <c r="N17" s="18"/>
@@ -31138,7 +31182,7 @@
     </row>
     <row r="18" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B18" s="15">
         <v>11.924099999999999</v>
@@ -31153,25 +31197,25 @@
         <v>9</v>
       </c>
       <c r="F18" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="G18" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="G18" s="14" t="s">
+      <c r="H18" s="14" t="s">
         <v>110</v>
-      </c>
-      <c r="H18" s="14" t="s">
-        <v>111</v>
       </c>
       <c r="I18" s="14">
         <v>600</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K18" s="14">
         <v>2021</v>
       </c>
       <c r="L18" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M18" s="18"/>
       <c r="N18" s="18"/>
@@ -31205,25 +31249,25 @@
         <v>9</v>
       </c>
       <c r="F19" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="H19" s="14" t="s">
         <v>113</v>
-      </c>
-      <c r="G19" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="H19" s="14" t="s">
-        <v>114</v>
       </c>
       <c r="I19" s="14">
         <v>180000</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K19" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="L19" s="14" t="s">
         <v>115</v>
-      </c>
-      <c r="L19" s="14" t="s">
-        <v>116</v>
       </c>
       <c r="M19" s="18"/>
       <c r="N19" s="18"/>
@@ -31257,25 +31301,25 @@
         <v>9</v>
       </c>
       <c r="F20" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="H20" s="14" t="s">
         <v>117</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="H20" s="14" t="s">
-        <v>118</v>
       </c>
       <c r="I20" s="14">
         <v>130000</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K20" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="L20" s="14" t="s">
         <v>115</v>
-      </c>
-      <c r="L20" s="14" t="s">
-        <v>116</v>
       </c>
       <c r="M20" s="18"/>
       <c r="N20" s="18"/>
@@ -31309,25 +31353,25 @@
         <v>9</v>
       </c>
       <c r="F21" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="H21" s="14" t="s">
         <v>119</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="H21" s="14" t="s">
-        <v>120</v>
       </c>
       <c r="I21" s="14">
         <v>421000</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K21" s="14">
         <v>2021</v>
       </c>
       <c r="L21" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M21" s="18"/>
       <c r="N21" s="18"/>
@@ -31361,25 +31405,25 @@
         <v>9</v>
       </c>
       <c r="F22" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="H22" s="14" t="s">
         <v>121</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="H22" s="14" t="s">
-        <v>122</v>
       </c>
       <c r="I22" s="14">
         <v>730000</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K22" s="14">
         <v>2022</v>
       </c>
       <c r="L22" s="14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M22" s="18"/>
       <c r="N22" s="18"/>
@@ -31413,25 +31457,25 @@
         <v>9</v>
       </c>
       <c r="F23" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="H23" s="14" t="s">
         <v>124</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="H23" s="14" t="s">
-        <v>125</v>
       </c>
       <c r="I23" s="14">
         <v>110000</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K23" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="L23" s="14" t="s">
         <v>115</v>
-      </c>
-      <c r="L23" s="14" t="s">
-        <v>116</v>
       </c>
       <c r="M23" s="18"/>
       <c r="N23" s="18"/>
@@ -31465,25 +31509,25 @@
         <v>9</v>
       </c>
       <c r="F24" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="H24" s="14" t="s">
         <v>126</v>
-      </c>
-      <c r="G24" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>127</v>
       </c>
       <c r="I24" s="14">
         <v>93000</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K24" s="14">
         <v>2021</v>
       </c>
       <c r="L24" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M24" s="18"/>
       <c r="N24" s="18"/>
@@ -31517,25 +31561,25 @@
         <v>9</v>
       </c>
       <c r="F25" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="G25" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="H25" s="14" t="s">
         <v>128</v>
-      </c>
-      <c r="G25" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="H25" s="14" t="s">
-        <v>129</v>
       </c>
       <c r="I25" s="14">
         <v>150000</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K25" s="14">
         <v>2021</v>
       </c>
       <c r="L25" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M25" s="18"/>
       <c r="N25" s="18"/>
@@ -31569,25 +31613,25 @@
         <v>9</v>
       </c>
       <c r="F26" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="H26" s="14" t="s">
         <v>130</v>
-      </c>
-      <c r="G26" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="H26" s="14" t="s">
-        <v>131</v>
       </c>
       <c r="I26" s="14">
         <v>100000</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K26" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="L26" s="14" t="s">
         <v>115</v>
-      </c>
-      <c r="L26" s="14" t="s">
-        <v>116</v>
       </c>
       <c r="M26" s="18"/>
       <c r="N26" s="18"/>
@@ -31621,25 +31665,25 @@
         <v>9</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I27" s="14">
         <v>540000</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K27" s="14">
         <v>2021</v>
       </c>
       <c r="L27" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M27" s="18"/>
       <c r="N27" s="18"/>
@@ -31673,25 +31717,25 @@
         <v>9</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G28" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="H28" s="14" t="s">
         <v>133</v>
-      </c>
-      <c r="H28" s="14" t="s">
-        <v>134</v>
       </c>
       <c r="I28" s="14">
         <v>160000</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K28" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="L28" s="14" t="s">
         <v>115</v>
-      </c>
-      <c r="L28" s="14" t="s">
-        <v>116</v>
       </c>
       <c r="M28" s="18"/>
       <c r="N28" s="18"/>
@@ -31725,25 +31769,25 @@
         <v>9</v>
       </c>
       <c r="F29" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="G29" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="H29" s="14" t="s">
         <v>135</v>
-      </c>
-      <c r="G29" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="H29" s="14" t="s">
-        <v>136</v>
       </c>
       <c r="I29" s="14">
         <v>174900</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K29" s="14">
         <v>2021</v>
       </c>
       <c r="L29" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M29" s="18"/>
       <c r="N29" s="18"/>
@@ -31777,25 +31821,25 @@
         <v>9</v>
       </c>
       <c r="F30" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="H30" s="14" t="s">
         <v>137</v>
-      </c>
-      <c r="G30" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="H30" s="14" t="s">
-        <v>138</v>
       </c>
       <c r="I30" s="14">
         <v>93400</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K30" s="14">
         <v>2021</v>
       </c>
       <c r="L30" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M30" s="18"/>
       <c r="N30" s="18"/>
@@ -31814,7 +31858,7 @@
     </row>
     <row r="31" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B31" s="15">
         <v>13.80006</v>
@@ -31829,25 +31873,25 @@
         <v>9</v>
       </c>
       <c r="F31" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="G31" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="G31" s="14" t="s">
-        <v>110</v>
-      </c>
       <c r="H31" s="14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I31" s="14">
         <v>612</v>
       </c>
       <c r="J31" s="14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K31" s="14">
         <v>2021</v>
       </c>
       <c r="L31" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M31" s="18"/>
       <c r="N31" s="18"/>
@@ -31866,7 +31910,7 @@
     </row>
     <row r="32" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B32" s="15">
         <v>12.63189</v>
@@ -31881,25 +31925,25 @@
         <v>9</v>
       </c>
       <c r="F32" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="H32" s="14" t="s">
         <v>140</v>
-      </c>
-      <c r="G32" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="H32" s="14" t="s">
-        <v>141</v>
       </c>
       <c r="I32" s="14">
         <v>150000</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K32" s="14">
         <v>2021</v>
       </c>
       <c r="L32" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M32" s="18"/>
       <c r="N32" s="18"/>
@@ -31918,7 +31962,7 @@
     </row>
     <row r="33" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B33" s="15">
         <v>11.556369999999999</v>
@@ -31933,25 +31977,25 @@
         <v>9</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H33" s="14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I33" s="14">
         <v>153333.33333333331</v>
       </c>
       <c r="J33" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K33" s="14">
         <v>2021</v>
       </c>
       <c r="L33" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M33" s="18"/>
       <c r="N33" s="18"/>
@@ -31970,7 +32014,7 @@
     </row>
     <row r="34" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B34" s="15">
         <v>12.08798</v>
@@ -31985,25 +32029,25 @@
         <v>9</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H34" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I34" s="14">
         <v>120000</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K34" s="14">
         <v>2021</v>
       </c>
       <c r="L34" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M34" s="18"/>
       <c r="N34" s="18"/>
@@ -32022,7 +32066,7 @@
     </row>
     <row r="35" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B35" s="15">
         <v>11.428890000000001</v>
@@ -32037,25 +32081,25 @@
         <v>9</v>
       </c>
       <c r="F35" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="H35" s="14" t="s">
         <v>145</v>
-      </c>
-      <c r="G35" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="H35" s="14" t="s">
-        <v>146</v>
       </c>
       <c r="I35" s="14">
         <v>222000</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K35" s="14">
         <v>2021</v>
       </c>
       <c r="L35" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M35" s="18"/>
       <c r="N35" s="18"/>
@@ -32089,25 +32133,25 @@
         <v>9</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H36" s="14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I36" s="14">
         <v>203125</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K36" s="14">
         <v>2021</v>
       </c>
       <c r="L36" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M36" s="18"/>
       <c r="N36" s="18"/>
@@ -32141,25 +32185,25 @@
         <v>9</v>
       </c>
       <c r="F37" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="G37" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="G37" s="14" t="s">
+      <c r="H37" s="14" t="s">
         <v>149</v>
-      </c>
-      <c r="H37" s="14" t="s">
-        <v>150</v>
       </c>
       <c r="I37" s="14">
         <v>195000</v>
       </c>
       <c r="J37" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K37" s="14">
         <v>2021</v>
       </c>
       <c r="L37" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M37" s="18"/>
       <c r="N37" s="18"/>
@@ -32193,25 +32237,25 @@
         <v>9</v>
       </c>
       <c r="F38" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="G38" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="H38" s="14" t="s">
         <v>151</v>
-      </c>
-      <c r="G38" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="H38" s="14" t="s">
-        <v>152</v>
       </c>
       <c r="I38" s="14">
         <v>380000</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K38" s="14">
         <v>2021</v>
       </c>
       <c r="L38" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M38" s="18"/>
       <c r="N38" s="18"/>
@@ -32230,7 +32274,7 @@
     </row>
     <row r="39" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B39" s="15">
         <v>9.7325099999999996</v>
@@ -32245,25 +32289,25 @@
         <v>9</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G39" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H39" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I39" s="14">
         <v>120000</v>
       </c>
       <c r="J39" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K39" s="14">
         <v>2021</v>
       </c>
       <c r="L39" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M39" s="18"/>
       <c r="N39" s="18"/>
@@ -32282,24 +32326,24 @@
     </row>
     <row r="40" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="26" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="42" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="43" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B43" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C43" s="19" t="s">
         <v>64</v>
-      </c>
-      <c r="C43" s="19" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="44" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B44" s="4">
         <v>12.053710000000001</v>
@@ -32310,7 +32354,7 @@
     </row>
     <row r="45" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B45" s="4">
         <v>11.69642</v>
@@ -32321,7 +32365,7 @@
     </row>
     <row r="46" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B46" s="4">
         <v>10.748810000000001</v>
@@ -32332,7 +32376,7 @@
     </row>
     <row r="47" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B47" s="4">
         <v>9.0727600000000006</v>
@@ -32354,7 +32398,7 @@
     </row>
     <row r="49" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B49" s="4">
         <v>8.3271999999999995</v>
@@ -32365,7 +32409,7 @@
     </row>
     <row r="50" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B50" s="4">
         <v>8.6266800000000003</v>
@@ -32376,7 +32420,7 @@
     </row>
     <row r="51" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B51" s="4">
         <v>8.4164499999999993</v>
@@ -32387,7 +32431,7 @@
     </row>
     <row r="52" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B52" s="4">
         <v>9.1895100000000003</v>
@@ -32398,7 +32442,7 @@
     </row>
     <row r="53" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B53" s="4">
         <v>7.6868600000000002</v>
@@ -32409,7 +32453,7 @@
     </row>
     <row r="54" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B54" s="4">
         <v>8.9330499999999997</v>
@@ -32420,7 +32464,7 @@
     </row>
     <row r="55" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B55" s="4">
         <v>10.991619999999999</v>
@@ -32431,7 +32475,7 @@
     </row>
     <row r="56" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B56" s="4">
         <v>11.338749999999999</v>
@@ -32442,7 +32486,7 @@
     </row>
     <row r="57" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B57" s="4">
         <v>13.77692</v>
@@ -32465,18 +32509,18 @@
     <row r="59" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="60" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="21" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B60" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C60" s="22" t="s">
         <v>64</v>
-      </c>
-      <c r="C60" s="22" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B61" s="2">
         <v>12.274480000000001</v>
@@ -32492,18 +32536,18 @@
     </row>
     <row r="63" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B63" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="C63" s="25" t="s">
         <v>64</v>
-      </c>
-      <c r="C63" s="25" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B64" s="5">
         <v>12.564</v>
@@ -32515,18 +32559,18 @@
     <row r="65" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="66" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="22" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B66" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C66" s="22" t="s">
         <v>64</v>
-      </c>
-      <c r="C66" s="22" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B67" s="4">
         <v>10.64</v>

--- a/southern_europe/italy_data/geographical_feature/node_metrics_paper.xlsx
+++ b/southern_europe/italy_data/geographical_feature/node_metrics_paper.xlsx
@@ -1,18 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nodes" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="truck" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pipeline" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="railway" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="raw_data" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="readme" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="truck_availability" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="nodes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="truck" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="pipeline" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="railway" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="raw_data" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="readme" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="truck_availability" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="paper_names" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'nodes'!$H$1:$H$48</definedName>
@@ -29,7 +30,7 @@
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Aptos Narrow"/>
       <color theme="1"/>
@@ -133,6 +134,9 @@
       <b val="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -194,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -237,6 +241,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -41942,4 +41947,1302 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="40" t="inlineStr">
+        <is>
+          <t>node_id</t>
+        </is>
+      </c>
+      <c r="B1" s="40" t="inlineStr">
+        <is>
+          <t>node_name</t>
+        </is>
+      </c>
+      <c r="C1" s="40" t="inlineStr">
+        <is>
+          <t>node_type</t>
+        </is>
+      </c>
+      <c r="D1" s="40" t="inlineStr">
+        <is>
+          <t>paper_name</t>
+        </is>
+      </c>
+      <c r="E1" s="40" t="inlineStr">
+        <is>
+          <t>sector_in_paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TRM - TERMOVALORIZZATORE DEL GERBIDO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Waste</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Torino WtE plant</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>WtE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ROBILANTE cement plant</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Robilante cement plant</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Trino Vercellese</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Trino Vercellese rail terminal</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Colacem - Stabilimento di Caravate</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Caravate cement plant</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Holcim (Italia) S.p.A.-unità produttiva di Ternate</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ternate cement plant</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TERMOVALORIZZATORE BUSTO ARSIZIO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Waste</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Busto Arsizio WtE plant</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>WtE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>RAFFINERIA SARPOM DI TRECATE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Refining</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Trecate refinery</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Refining</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LOMELLINA ENERGIA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Waste</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Parona WtE plant</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>WtE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>RAFFINERIA DI SANNAZZARO DE' BURGONDI</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Refining</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sannazzaro de' Burgondi refinery</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Refining</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Iplom S.p.A - Raffineria di Busalla</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Refining</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Busalla refinery</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Refining</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TERMOVALORIZZATORE COMO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Waste</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Como WtE plant</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>WtE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TERMOVALORIZZATORE DI DESIO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Waste</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Desio WtE plant</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>WtE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SILLA 2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Waste</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Milano WtE plant</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>WtE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TermoTrezzo</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Waste</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Trezzo sull'Adda WtE plant</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>WtE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Segrate</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Segrate rail terminal</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TERMOVALORIZZATORE DI CORTEOLONA E GENZONE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Waste</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Corteolona WtE plant</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>WtE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Impianto di termovalorizzazione di Valmadrera</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Waste</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Valmadrera WtE plant</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>WtE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Italcementi Calusco D'Adda</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Calusco d'Adda cement plant</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Termovalorizzatore di Dalmine</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Waste</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Dalmine WtE plant</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>WtE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Piacenza</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Waste</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Piacenza WtE plant</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>WtE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Piacenza</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Piacenza cement plant</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>VERNASCA cement plant</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Vernasca cement plant</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Stabilimento di Tavernola Bergamasca</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Tavernola Bergamasca cement plant</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TERMOVALORIZZATORE DI BRESCIA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Waste</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Brescia WtE plant</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>WtE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Italcementi di Rezzato</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Rezzato cement plant</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TERMOVALORIZZATORE - PAIP</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Waste</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Parma WtE plant</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>WtE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TERMOVALORIZZAOTRE DI VERONA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Waste</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Verona WtE plant</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>WtE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>HERAMBIENTE S.R.L.  - Termovalorizzatore</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Waste</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Modena WtE plant</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>WtE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>TERMOVALORIZZATORE DI BOLZANO</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Waste</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Bolzano WtE plant</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>WtE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Ferrara</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Waste</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Ferrara WtE plant</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>WtE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ferrara</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>FertilizersCombustion</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Ferrara fertiliser plant (combustion)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Fertilisers</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ferrara</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>FertilizersSMR</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Ferrara fertiliser plant (SMR)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Fertilisers</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>FRULLO ENERGIA AMBIENTE S.R.L.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Waste</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Granarolo dell'Emilia WtE plant</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>WtE</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>MONSELICE cement plant</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Monselice cement plant</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Fassa Cerano Dolce</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Lime</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Dolcè lime plant</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Lime</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Cementirossi - Cementeria di Pederobba</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Pederobba cement plant</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Impianto di Termovalorizzazione di San Lazzaro (PD)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Waste</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Padova WtE plant</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>WtE</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>HERAMBIENTE - 3^ LINEA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Waste</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Forlì WtE plant</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>WtE</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>STABILIMENTO DI PONTE DELLA PRIULA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Susegana cement plant</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Ravenna</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Ravenna industrial cluster</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Venezia Marghera Scalo</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Venezia Marghera rail terminal</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>FANNA cement plant</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Fanna cement plant</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Termovalorizzatore di Rimini</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Waste</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Rimini WtE plant</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>WtE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Impianto di Termovalorizzazione Rifiuti di Trieste</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Waste</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Trieste WtE plant</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>WtE</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Eni S.p.A Casalborsetti</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Casalborsetti onshore terminal</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Porto Corsini</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Porto Corsini offshore storage</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Modena-H</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Modena transport hub</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Unicalce Val Brembilla Lime</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Lime</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Val Brembilla lime plant</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Lime</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Fassa Montichiari Lime</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Lime</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Montichiari lime plant</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Lime</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Unicalce Bernezzo</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Lime</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bernezzo lime plant</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Lime</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>